--- a/docs/Mapping_casi_uso/matrimoni/Matr_008.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_008.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3626" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3626" uniqueCount="322">
   <si>
     <t>Sezione</t>
   </si>
@@ -800,7 +800,10 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
+  </si>
+  <si>
+    <t>Firmatario</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -809,7 +812,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -818,7 +821,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -827,7 +830,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -836,13 +839,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposo</t>
@@ -851,7 +854,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Tutore Sposa</t>
@@ -860,13 +863,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposa</t>
@@ -875,7 +878,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Dettagli evento</t>
@@ -935,13 +938,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1042,7 +1045,7 @@
     <col min="4" max="4" width="62.65625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.0546875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="114.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7766,10 +7769,10 @@
         <v>260</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>261</v>
@@ -7786,7 +7789,7 @@
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>90</v>
@@ -7795,7 +7798,7 @@
         <v>9</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>92</v>
@@ -7804,12 +7807,12 @@
         <v>10</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>93</v>
@@ -7818,7 +7821,7 @@
         <v>52</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>94</v>
@@ -7827,12 +7830,12 @@
         <v>10</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>95</v>
@@ -7841,7 +7844,7 @@
         <v>9</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>96</v>
@@ -7850,12 +7853,12 @@
         <v>10</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>97</v>
@@ -7864,7 +7867,7 @@
         <v>52</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>98</v>
@@ -7873,12 +7876,12 @@
         <v>10</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>99</v>
@@ -7887,7 +7890,7 @@
         <v>9</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>100</v>
@@ -7896,12 +7899,12 @@
         <v>10</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>101</v>
@@ -7910,7 +7913,7 @@
         <v>9</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>102</v>
@@ -7919,12 +7922,12 @@
         <v>10</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>103</v>
@@ -7933,7 +7936,7 @@
         <v>52</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>104</v>
@@ -7942,12 +7945,12 @@
         <v>10</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>105</v>
@@ -7956,7 +7959,7 @@
         <v>52</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>106</v>
@@ -7965,12 +7968,12 @@
         <v>10</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>107</v>
@@ -7979,7 +7982,7 @@
         <v>52</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>108</v>
@@ -7988,12 +7991,12 @@
         <v>10</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>109</v>
@@ -8002,7 +8005,7 @@
         <v>9</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>110</v>
@@ -8011,12 +8014,12 @@
         <v>10</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>111</v>
@@ -8025,7 +8028,7 @@
         <v>9</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>112</v>
@@ -8034,12 +8037,12 @@
         <v>10</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>113</v>
@@ -8048,7 +8051,7 @@
         <v>9</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>114</v>
@@ -8057,12 +8060,12 @@
         <v>10</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>115</v>
@@ -8071,7 +8074,7 @@
         <v>9</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>116</v>
@@ -8080,12 +8083,12 @@
         <v>10</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>117</v>
@@ -8094,7 +8097,7 @@
         <v>9</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>118</v>
@@ -8103,12 +8106,12 @@
         <v>10</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>119</v>
@@ -8117,7 +8120,7 @@
         <v>52</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>120</v>
@@ -8126,12 +8129,12 @@
         <v>10</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>121</v>
@@ -8140,7 +8143,7 @@
         <v>52</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>122</v>
@@ -8149,12 +8152,12 @@
         <v>10</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>123</v>
@@ -8163,7 +8166,7 @@
         <v>9</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>124</v>
@@ -8172,12 +8175,12 @@
         <v>10</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>125</v>
@@ -8186,7 +8189,7 @@
         <v>9</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>126</v>
@@ -8195,12 +8198,12 @@
         <v>10</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>127</v>
@@ -8209,7 +8212,7 @@
         <v>9</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>128</v>
@@ -8218,12 +8221,12 @@
         <v>10</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>129</v>
@@ -8232,7 +8235,7 @@
         <v>9</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>130</v>
@@ -8241,12 +8244,12 @@
         <v>10</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>131</v>
@@ -8255,7 +8258,7 @@
         <v>9</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>132</v>
@@ -8264,12 +8267,12 @@
         <v>10</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>133</v>
@@ -8278,7 +8281,7 @@
         <v>9</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>134</v>
@@ -8287,12 +8290,12 @@
         <v>10</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>135</v>
@@ -8301,7 +8304,7 @@
         <v>9</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>136</v>
@@ -8310,12 +8313,12 @@
         <v>10</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>137</v>
@@ -8324,7 +8327,7 @@
         <v>9</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>138</v>
@@ -8333,12 +8336,12 @@
         <v>10</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>139</v>
@@ -8347,7 +8350,7 @@
         <v>9</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>140</v>
@@ -8356,12 +8359,12 @@
         <v>10</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>141</v>
@@ -8370,7 +8373,7 @@
         <v>52</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>142</v>
@@ -8379,12 +8382,12 @@
         <v>10</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>143</v>
@@ -8393,7 +8396,7 @@
         <v>52</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>144</v>
@@ -8402,21 +8405,21 @@
         <v>10</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B321" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="C321" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>146</v>
@@ -8425,12 +8428,12 @@
         <v>10</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>90</v>
@@ -8439,7 +8442,7 @@
         <v>9</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>92</v>
@@ -8448,12 +8451,12 @@
         <v>10</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>93</v>
@@ -8462,7 +8465,7 @@
         <v>52</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>94</v>
@@ -8471,12 +8474,12 @@
         <v>10</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>95</v>
@@ -8485,7 +8488,7 @@
         <v>9</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>96</v>
@@ -8494,12 +8497,12 @@
         <v>10</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>97</v>
@@ -8508,7 +8511,7 @@
         <v>52</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>98</v>
@@ -8517,12 +8520,12 @@
         <v>10</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>99</v>
@@ -8531,7 +8534,7 @@
         <v>9</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>100</v>
@@ -8540,12 +8543,12 @@
         <v>10</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>101</v>
@@ -8554,7 +8557,7 @@
         <v>9</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>102</v>
@@ -8563,12 +8566,12 @@
         <v>10</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>103</v>
@@ -8577,7 +8580,7 @@
         <v>52</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>104</v>
@@ -8586,12 +8589,12 @@
         <v>10</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>105</v>
@@ -8600,7 +8603,7 @@
         <v>52</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>106</v>
@@ -8609,12 +8612,12 @@
         <v>10</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>107</v>
@@ -8623,7 +8626,7 @@
         <v>52</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>108</v>
@@ -8632,12 +8635,12 @@
         <v>10</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>109</v>
@@ -8646,7 +8649,7 @@
         <v>9</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>110</v>
@@ -8655,12 +8658,12 @@
         <v>10</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>111</v>
@@ -8669,7 +8672,7 @@
         <v>9</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>112</v>
@@ -8678,12 +8681,12 @@
         <v>10</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>113</v>
@@ -8692,7 +8695,7 @@
         <v>9</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>114</v>
@@ -8701,12 +8704,12 @@
         <v>10</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>115</v>
@@ -8715,7 +8718,7 @@
         <v>9</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>116</v>
@@ -8724,12 +8727,12 @@
         <v>10</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>117</v>
@@ -8738,7 +8741,7 @@
         <v>9</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>118</v>
@@ -8747,12 +8750,12 @@
         <v>10</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>119</v>
@@ -8761,7 +8764,7 @@
         <v>52</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>120</v>
@@ -8770,12 +8773,12 @@
         <v>10</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>121</v>
@@ -8784,7 +8787,7 @@
         <v>52</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>122</v>
@@ -8793,12 +8796,12 @@
         <v>10</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>123</v>
@@ -8807,7 +8810,7 @@
         <v>9</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>124</v>
@@ -8816,12 +8819,12 @@
         <v>10</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>125</v>
@@ -8830,7 +8833,7 @@
         <v>9</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>126</v>
@@ -8839,12 +8842,12 @@
         <v>10</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>127</v>
@@ -8853,7 +8856,7 @@
         <v>9</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>128</v>
@@ -8862,12 +8865,12 @@
         <v>10</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>129</v>
@@ -8876,7 +8879,7 @@
         <v>9</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>130</v>
@@ -8885,12 +8888,12 @@
         <v>10</v>
       </c>
       <c r="G341" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>131</v>
@@ -8899,7 +8902,7 @@
         <v>9</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>132</v>
@@ -8908,12 +8911,12 @@
         <v>10</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>133</v>
@@ -8922,7 +8925,7 @@
         <v>9</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>134</v>
@@ -8931,12 +8934,12 @@
         <v>10</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>135</v>
@@ -8945,7 +8948,7 @@
         <v>9</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>136</v>
@@ -8954,12 +8957,12 @@
         <v>10</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>137</v>
@@ -8968,7 +8971,7 @@
         <v>9</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>138</v>
@@ -8977,12 +8980,12 @@
         <v>10</v>
       </c>
       <c r="G345" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>139</v>
@@ -8991,7 +8994,7 @@
         <v>9</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>140</v>
@@ -9000,12 +9003,12 @@
         <v>10</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>141</v>
@@ -9014,7 +9017,7 @@
         <v>52</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>142</v>
@@ -9023,12 +9026,12 @@
         <v>10</v>
       </c>
       <c r="G347" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>143</v>
@@ -9037,7 +9040,7 @@
         <v>52</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>144</v>
@@ -9046,21 +9049,21 @@
         <v>10</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>146</v>
@@ -9069,12 +9072,12 @@
         <v>10</v>
       </c>
       <c r="G349" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>90</v>
@@ -9083,7 +9086,7 @@
         <v>9</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>92</v>
@@ -9092,12 +9095,12 @@
         <v>10</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>93</v>
@@ -9106,7 +9109,7 @@
         <v>52</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>94</v>
@@ -9115,12 +9118,12 @@
         <v>10</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>95</v>
@@ -9129,7 +9132,7 @@
         <v>9</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>96</v>
@@ -9138,12 +9141,12 @@
         <v>10</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>97</v>
@@ -9152,7 +9155,7 @@
         <v>52</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>98</v>
@@ -9161,12 +9164,12 @@
         <v>10</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>99</v>
@@ -9175,7 +9178,7 @@
         <v>9</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>100</v>
@@ -9184,12 +9187,12 @@
         <v>10</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>101</v>
@@ -9198,7 +9201,7 @@
         <v>9</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>102</v>
@@ -9207,12 +9210,12 @@
         <v>10</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>103</v>
@@ -9221,7 +9224,7 @@
         <v>52</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>104</v>
@@ -9230,12 +9233,12 @@
         <v>10</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>105</v>
@@ -9244,7 +9247,7 @@
         <v>52</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>106</v>
@@ -9253,12 +9256,12 @@
         <v>10</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>107</v>
@@ -9267,7 +9270,7 @@
         <v>52</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>108</v>
@@ -9276,12 +9279,12 @@
         <v>10</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>109</v>
@@ -9290,7 +9293,7 @@
         <v>9</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>110</v>
@@ -9299,12 +9302,12 @@
         <v>10</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>111</v>
@@ -9313,7 +9316,7 @@
         <v>9</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>112</v>
@@ -9322,12 +9325,12 @@
         <v>10</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>113</v>
@@ -9336,7 +9339,7 @@
         <v>9</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>114</v>
@@ -9345,12 +9348,12 @@
         <v>10</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>115</v>
@@ -9359,7 +9362,7 @@
         <v>9</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>116</v>
@@ -9368,12 +9371,12 @@
         <v>10</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>117</v>
@@ -9382,7 +9385,7 @@
         <v>9</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>118</v>
@@ -9391,12 +9394,12 @@
         <v>10</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>119</v>
@@ -9405,7 +9408,7 @@
         <v>52</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>120</v>
@@ -9414,12 +9417,12 @@
         <v>10</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>121</v>
@@ -9428,7 +9431,7 @@
         <v>52</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>122</v>
@@ -9437,12 +9440,12 @@
         <v>10</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>123</v>
@@ -9451,7 +9454,7 @@
         <v>9</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>124</v>
@@ -9460,12 +9463,12 @@
         <v>10</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>125</v>
@@ -9474,7 +9477,7 @@
         <v>9</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>126</v>
@@ -9483,12 +9486,12 @@
         <v>10</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>127</v>
@@ -9497,7 +9500,7 @@
         <v>9</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>128</v>
@@ -9506,12 +9509,12 @@
         <v>10</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>129</v>
@@ -9520,7 +9523,7 @@
         <v>9</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>130</v>
@@ -9529,12 +9532,12 @@
         <v>10</v>
       </c>
       <c r="G369" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>131</v>
@@ -9543,7 +9546,7 @@
         <v>9</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>132</v>
@@ -9552,12 +9555,12 @@
         <v>10</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>133</v>
@@ -9566,7 +9569,7 @@
         <v>9</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>134</v>
@@ -9575,12 +9578,12 @@
         <v>10</v>
       </c>
       <c r="G371" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>135</v>
@@ -9589,7 +9592,7 @@
         <v>9</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>136</v>
@@ -9598,12 +9601,12 @@
         <v>10</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>137</v>
@@ -9612,7 +9615,7 @@
         <v>9</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>138</v>
@@ -9621,12 +9624,12 @@
         <v>10</v>
       </c>
       <c r="G373" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>139</v>
@@ -9635,7 +9638,7 @@
         <v>9</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>140</v>
@@ -9644,12 +9647,12 @@
         <v>10</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>141</v>
@@ -9658,7 +9661,7 @@
         <v>52</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>142</v>
@@ -9667,12 +9670,12 @@
         <v>10</v>
       </c>
       <c r="G375" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>143</v>
@@ -9681,7 +9684,7 @@
         <v>52</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>144</v>
@@ -9690,21 +9693,21 @@
         <v>10</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>146</v>
@@ -9713,12 +9716,12 @@
         <v>10</v>
       </c>
       <c r="G377" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>90</v>
@@ -9727,7 +9730,7 @@
         <v>9</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E378" s="2" t="s">
         <v>92</v>
@@ -9736,12 +9739,12 @@
         <v>10</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>93</v>
@@ -9750,7 +9753,7 @@
         <v>52</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>94</v>
@@ -9759,12 +9762,12 @@
         <v>10</v>
       </c>
       <c r="G379" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>95</v>
@@ -9773,7 +9776,7 @@
         <v>9</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>96</v>
@@ -9782,12 +9785,12 @@
         <v>10</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>97</v>
@@ -9796,7 +9799,7 @@
         <v>52</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>98</v>
@@ -9805,12 +9808,12 @@
         <v>10</v>
       </c>
       <c r="G381" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>99</v>
@@ -9819,7 +9822,7 @@
         <v>9</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>100</v>
@@ -9828,12 +9831,12 @@
         <v>10</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>101</v>
@@ -9842,7 +9845,7 @@
         <v>9</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>102</v>
@@ -9851,12 +9854,12 @@
         <v>10</v>
       </c>
       <c r="G383" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>103</v>
@@ -9865,7 +9868,7 @@
         <v>52</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>104</v>
@@ -9874,12 +9877,12 @@
         <v>10</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>105</v>
@@ -9888,7 +9891,7 @@
         <v>52</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E385" s="2" t="s">
         <v>106</v>
@@ -9897,12 +9900,12 @@
         <v>10</v>
       </c>
       <c r="G385" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>107</v>
@@ -9911,7 +9914,7 @@
         <v>52</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>108</v>
@@ -9920,12 +9923,12 @@
         <v>10</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>109</v>
@@ -9934,7 +9937,7 @@
         <v>9</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E387" s="2" t="s">
         <v>110</v>
@@ -9943,12 +9946,12 @@
         <v>10</v>
       </c>
       <c r="G387" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>111</v>
@@ -9957,7 +9960,7 @@
         <v>9</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E388" s="2" t="s">
         <v>112</v>
@@ -9966,12 +9969,12 @@
         <v>10</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>113</v>
@@ -9980,7 +9983,7 @@
         <v>9</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>114</v>
@@ -9989,12 +9992,12 @@
         <v>10</v>
       </c>
       <c r="G389" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>115</v>
@@ -10003,7 +10006,7 @@
         <v>9</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>116</v>
@@ -10012,12 +10015,12 @@
         <v>10</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>117</v>
@@ -10026,7 +10029,7 @@
         <v>9</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>118</v>
@@ -10035,12 +10038,12 @@
         <v>10</v>
       </c>
       <c r="G391" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>119</v>
@@ -10049,7 +10052,7 @@
         <v>52</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>120</v>
@@ -10058,12 +10061,12 @@
         <v>10</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>121</v>
@@ -10072,7 +10075,7 @@
         <v>52</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>122</v>
@@ -10081,12 +10084,12 @@
         <v>10</v>
       </c>
       <c r="G393" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>123</v>
@@ -10095,7 +10098,7 @@
         <v>9</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>124</v>
@@ -10104,12 +10107,12 @@
         <v>10</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>125</v>
@@ -10118,7 +10121,7 @@
         <v>9</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>126</v>
@@ -10127,12 +10130,12 @@
         <v>10</v>
       </c>
       <c r="G395" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>127</v>
@@ -10141,7 +10144,7 @@
         <v>9</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E396" s="2" t="s">
         <v>128</v>
@@ -10150,12 +10153,12 @@
         <v>10</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>129</v>
@@ -10164,7 +10167,7 @@
         <v>9</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>130</v>
@@ -10173,12 +10176,12 @@
         <v>10</v>
       </c>
       <c r="G397" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>131</v>
@@ -10187,7 +10190,7 @@
         <v>9</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>132</v>
@@ -10196,12 +10199,12 @@
         <v>10</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>133</v>
@@ -10210,7 +10213,7 @@
         <v>9</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E399" s="2" t="s">
         <v>134</v>
@@ -10219,12 +10222,12 @@
         <v>10</v>
       </c>
       <c r="G399" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>135</v>
@@ -10233,7 +10236,7 @@
         <v>9</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>136</v>
@@ -10242,12 +10245,12 @@
         <v>10</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>137</v>
@@ -10256,7 +10259,7 @@
         <v>9</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>138</v>
@@ -10265,12 +10268,12 @@
         <v>10</v>
       </c>
       <c r="G401" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>139</v>
@@ -10279,7 +10282,7 @@
         <v>9</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>140</v>
@@ -10288,12 +10291,12 @@
         <v>10</v>
       </c>
       <c r="G402" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>141</v>
@@ -10302,7 +10305,7 @@
         <v>52</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>142</v>
@@ -10311,12 +10314,12 @@
         <v>10</v>
       </c>
       <c r="G403" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>143</v>
@@ -10325,7 +10328,7 @@
         <v>52</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>144</v>
@@ -10334,21 +10337,21 @@
         <v>10</v>
       </c>
       <c r="G404" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>146</v>
@@ -10357,12 +10360,12 @@
         <v>10</v>
       </c>
       <c r="G405" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>90</v>
@@ -10371,7 +10374,7 @@
         <v>9</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>92</v>
@@ -10380,12 +10383,12 @@
         <v>10</v>
       </c>
       <c r="G406" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>93</v>
@@ -10394,7 +10397,7 @@
         <v>52</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>94</v>
@@ -10403,12 +10406,12 @@
         <v>10</v>
       </c>
       <c r="G407" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>95</v>
@@ -10417,7 +10420,7 @@
         <v>9</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>96</v>
@@ -10426,12 +10429,12 @@
         <v>10</v>
       </c>
       <c r="G408" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>97</v>
@@ -10440,7 +10443,7 @@
         <v>52</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>98</v>
@@ -10449,12 +10452,12 @@
         <v>10</v>
       </c>
       <c r="G409" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>99</v>
@@ -10463,7 +10466,7 @@
         <v>9</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>100</v>
@@ -10472,12 +10475,12 @@
         <v>10</v>
       </c>
       <c r="G410" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>101</v>
@@ -10486,7 +10489,7 @@
         <v>9</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E411" s="2" t="s">
         <v>102</v>
@@ -10495,12 +10498,12 @@
         <v>10</v>
       </c>
       <c r="G411" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>103</v>
@@ -10509,7 +10512,7 @@
         <v>52</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>104</v>
@@ -10518,12 +10521,12 @@
         <v>10</v>
       </c>
       <c r="G412" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>105</v>
@@ -10532,7 +10535,7 @@
         <v>52</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>106</v>
@@ -10541,12 +10544,12 @@
         <v>10</v>
       </c>
       <c r="G413" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>107</v>
@@ -10555,7 +10558,7 @@
         <v>52</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>108</v>
@@ -10564,12 +10567,12 @@
         <v>10</v>
       </c>
       <c r="G414" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>109</v>
@@ -10578,7 +10581,7 @@
         <v>9</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E415" s="2" t="s">
         <v>110</v>
@@ -10587,12 +10590,12 @@
         <v>10</v>
       </c>
       <c r="G415" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>111</v>
@@ -10601,7 +10604,7 @@
         <v>9</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>112</v>
@@ -10610,12 +10613,12 @@
         <v>10</v>
       </c>
       <c r="G416" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>113</v>
@@ -10624,7 +10627,7 @@
         <v>9</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>114</v>
@@ -10633,12 +10636,12 @@
         <v>10</v>
       </c>
       <c r="G417" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>115</v>
@@ -10647,7 +10650,7 @@
         <v>9</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E418" s="2" t="s">
         <v>116</v>
@@ -10656,12 +10659,12 @@
         <v>10</v>
       </c>
       <c r="G418" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>117</v>
@@ -10670,7 +10673,7 @@
         <v>9</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>118</v>
@@ -10679,12 +10682,12 @@
         <v>10</v>
       </c>
       <c r="G419" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>119</v>
@@ -10693,7 +10696,7 @@
         <v>52</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E420" s="2" t="s">
         <v>120</v>
@@ -10702,12 +10705,12 @@
         <v>10</v>
       </c>
       <c r="G420" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>121</v>
@@ -10716,7 +10719,7 @@
         <v>52</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E421" s="2" t="s">
         <v>122</v>
@@ -10725,12 +10728,12 @@
         <v>10</v>
       </c>
       <c r="G421" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>123</v>
@@ -10739,7 +10742,7 @@
         <v>9</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E422" s="2" t="s">
         <v>124</v>
@@ -10748,12 +10751,12 @@
         <v>10</v>
       </c>
       <c r="G422" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>125</v>
@@ -10762,7 +10765,7 @@
         <v>9</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>126</v>
@@ -10771,12 +10774,12 @@
         <v>10</v>
       </c>
       <c r="G423" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>127</v>
@@ -10785,7 +10788,7 @@
         <v>9</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>128</v>
@@ -10794,12 +10797,12 @@
         <v>10</v>
       </c>
       <c r="G424" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>129</v>
@@ -10808,7 +10811,7 @@
         <v>9</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>130</v>
@@ -10817,12 +10820,12 @@
         <v>10</v>
       </c>
       <c r="G425" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>131</v>
@@ -10831,7 +10834,7 @@
         <v>9</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>132</v>
@@ -10840,12 +10843,12 @@
         <v>10</v>
       </c>
       <c r="G426" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>133</v>
@@ -10854,7 +10857,7 @@
         <v>9</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E427" s="2" t="s">
         <v>134</v>
@@ -10863,12 +10866,12 @@
         <v>10</v>
       </c>
       <c r="G427" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>135</v>
@@ -10877,7 +10880,7 @@
         <v>9</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E428" s="2" t="s">
         <v>136</v>
@@ -10886,12 +10889,12 @@
         <v>10</v>
       </c>
       <c r="G428" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>137</v>
@@ -10900,7 +10903,7 @@
         <v>9</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>138</v>
@@ -10909,12 +10912,12 @@
         <v>10</v>
       </c>
       <c r="G429" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>139</v>
@@ -10923,7 +10926,7 @@
         <v>9</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E430" s="2" t="s">
         <v>140</v>
@@ -10932,12 +10935,12 @@
         <v>10</v>
       </c>
       <c r="G430" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>141</v>
@@ -10946,7 +10949,7 @@
         <v>52</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>142</v>
@@ -10955,12 +10958,12 @@
         <v>10</v>
       </c>
       <c r="G431" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>143</v>
@@ -10969,7 +10972,7 @@
         <v>52</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>144</v>
@@ -10978,21 +10981,21 @@
         <v>10</v>
       </c>
       <c r="G432" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>146</v>
@@ -11001,12 +11004,12 @@
         <v>10</v>
       </c>
       <c r="G433" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>213</v>
@@ -11015,7 +11018,7 @@
         <v>52</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>215</v>
@@ -11024,12 +11027,12 @@
         <v>10</v>
       </c>
       <c r="G434" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>217</v>
@@ -11038,7 +11041,7 @@
         <v>52</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>218</v>
@@ -11047,12 +11050,12 @@
         <v>10</v>
       </c>
       <c r="G435" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>219</v>
@@ -11061,7 +11064,7 @@
         <v>52</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>220</v>
@@ -11070,12 +11073,12 @@
         <v>10</v>
       </c>
       <c r="G436" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>221</v>
@@ -11084,7 +11087,7 @@
         <v>52</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>222</v>
@@ -11093,12 +11096,12 @@
         <v>10</v>
       </c>
       <c r="G437" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>223</v>
@@ -11107,7 +11110,7 @@
         <v>52</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>224</v>
@@ -11116,12 +11119,12 @@
         <v>10</v>
       </c>
       <c r="G438" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>225</v>
@@ -11130,7 +11133,7 @@
         <v>52</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>226</v>
@@ -11139,12 +11142,12 @@
         <v>10</v>
       </c>
       <c r="G439" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>227</v>
@@ -11153,7 +11156,7 @@
         <v>52</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>228</v>
@@ -11162,12 +11165,12 @@
         <v>10</v>
       </c>
       <c r="G440" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>90</v>
@@ -11176,7 +11179,7 @@
         <v>9</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>92</v>
@@ -11185,12 +11188,12 @@
         <v>10</v>
       </c>
       <c r="G441" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>93</v>
@@ -11199,7 +11202,7 @@
         <v>52</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>94</v>
@@ -11208,12 +11211,12 @@
         <v>10</v>
       </c>
       <c r="G442" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>95</v>
@@ -11222,7 +11225,7 @@
         <v>9</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>96</v>
@@ -11231,12 +11234,12 @@
         <v>10</v>
       </c>
       <c r="G443" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>97</v>
@@ -11245,7 +11248,7 @@
         <v>52</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>98</v>
@@ -11254,12 +11257,12 @@
         <v>10</v>
       </c>
       <c r="G444" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>99</v>
@@ -11268,7 +11271,7 @@
         <v>9</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>100</v>
@@ -11277,12 +11280,12 @@
         <v>10</v>
       </c>
       <c r="G445" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>101</v>
@@ -11291,7 +11294,7 @@
         <v>9</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>102</v>
@@ -11300,12 +11303,12 @@
         <v>10</v>
       </c>
       <c r="G446" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>103</v>
@@ -11314,7 +11317,7 @@
         <v>52</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>104</v>
@@ -11323,12 +11326,12 @@
         <v>10</v>
       </c>
       <c r="G447" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>105</v>
@@ -11337,7 +11340,7 @@
         <v>52</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>106</v>
@@ -11346,12 +11349,12 @@
         <v>10</v>
       </c>
       <c r="G448" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>107</v>
@@ -11360,7 +11363,7 @@
         <v>52</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>108</v>
@@ -11369,12 +11372,12 @@
         <v>10</v>
       </c>
       <c r="G449" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>109</v>
@@ -11383,7 +11386,7 @@
         <v>9</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>110</v>
@@ -11392,12 +11395,12 @@
         <v>10</v>
       </c>
       <c r="G450" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>111</v>
@@ -11406,7 +11409,7 @@
         <v>9</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>112</v>
@@ -11415,12 +11418,12 @@
         <v>10</v>
       </c>
       <c r="G451" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>113</v>
@@ -11429,7 +11432,7 @@
         <v>9</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>114</v>
@@ -11438,12 +11441,12 @@
         <v>10</v>
       </c>
       <c r="G452" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>115</v>
@@ -11452,7 +11455,7 @@
         <v>9</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>116</v>
@@ -11461,12 +11464,12 @@
         <v>10</v>
       </c>
       <c r="G453" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>117</v>
@@ -11475,7 +11478,7 @@
         <v>9</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>118</v>
@@ -11484,12 +11487,12 @@
         <v>10</v>
       </c>
       <c r="G454" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>119</v>
@@ -11498,7 +11501,7 @@
         <v>52</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>120</v>
@@ -11507,12 +11510,12 @@
         <v>10</v>
       </c>
       <c r="G455" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>121</v>
@@ -11521,7 +11524,7 @@
         <v>52</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E456" s="2" t="s">
         <v>122</v>
@@ -11530,12 +11533,12 @@
         <v>10</v>
       </c>
       <c r="G456" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>123</v>
@@ -11544,7 +11547,7 @@
         <v>9</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E457" s="2" t="s">
         <v>124</v>
@@ -11553,12 +11556,12 @@
         <v>10</v>
       </c>
       <c r="G457" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>125</v>
@@ -11567,7 +11570,7 @@
         <v>9</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E458" s="2" t="s">
         <v>126</v>
@@ -11576,12 +11579,12 @@
         <v>10</v>
       </c>
       <c r="G458" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>127</v>
@@ -11590,7 +11593,7 @@
         <v>9</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>128</v>
@@ -11599,12 +11602,12 @@
         <v>10</v>
       </c>
       <c r="G459" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>129</v>
@@ -11613,7 +11616,7 @@
         <v>9</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>130</v>
@@ -11622,12 +11625,12 @@
         <v>10</v>
       </c>
       <c r="G460" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>131</v>
@@ -11636,7 +11639,7 @@
         <v>9</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>132</v>
@@ -11645,12 +11648,12 @@
         <v>10</v>
       </c>
       <c r="G461" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>133</v>
@@ -11659,7 +11662,7 @@
         <v>9</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>134</v>
@@ -11668,12 +11671,12 @@
         <v>10</v>
       </c>
       <c r="G462" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>135</v>
@@ -11682,7 +11685,7 @@
         <v>9</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E463" s="2" t="s">
         <v>136</v>
@@ -11691,12 +11694,12 @@
         <v>10</v>
       </c>
       <c r="G463" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>137</v>
@@ -11705,7 +11708,7 @@
         <v>9</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>138</v>
@@ -11714,12 +11717,12 @@
         <v>10</v>
       </c>
       <c r="G464" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>139</v>
@@ -11728,7 +11731,7 @@
         <v>9</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E465" s="2" t="s">
         <v>140</v>
@@ -11737,12 +11740,12 @@
         <v>10</v>
       </c>
       <c r="G465" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>141</v>
@@ -11751,7 +11754,7 @@
         <v>52</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>142</v>
@@ -11760,12 +11763,12 @@
         <v>10</v>
       </c>
       <c r="G466" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>143</v>
@@ -11774,7 +11777,7 @@
         <v>52</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E467" s="2" t="s">
         <v>144</v>
@@ -11783,21 +11786,21 @@
         <v>10</v>
       </c>
       <c r="G467" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>146</v>
@@ -11806,12 +11809,12 @@
         <v>10</v>
       </c>
       <c r="G468" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>90</v>
@@ -11820,7 +11823,7 @@
         <v>9</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>92</v>
@@ -11829,12 +11832,12 @@
         <v>10</v>
       </c>
       <c r="G469" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>93</v>
@@ -11843,7 +11846,7 @@
         <v>52</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E470" s="2" t="s">
         <v>94</v>
@@ -11852,12 +11855,12 @@
         <v>10</v>
       </c>
       <c r="G470" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>95</v>
@@ -11866,7 +11869,7 @@
         <v>9</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E471" s="2" t="s">
         <v>96</v>
@@ -11875,12 +11878,12 @@
         <v>10</v>
       </c>
       <c r="G471" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>97</v>
@@ -11889,7 +11892,7 @@
         <v>52</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>98</v>
@@ -11898,12 +11901,12 @@
         <v>10</v>
       </c>
       <c r="G472" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>99</v>
@@ -11912,7 +11915,7 @@
         <v>9</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>100</v>
@@ -11921,12 +11924,12 @@
         <v>10</v>
       </c>
       <c r="G473" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>101</v>
@@ -11935,7 +11938,7 @@
         <v>9</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>102</v>
@@ -11944,12 +11947,12 @@
         <v>10</v>
       </c>
       <c r="G474" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>103</v>
@@ -11958,7 +11961,7 @@
         <v>52</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E475" s="2" t="s">
         <v>104</v>
@@ -11967,12 +11970,12 @@
         <v>10</v>
       </c>
       <c r="G475" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>105</v>
@@ -11981,7 +11984,7 @@
         <v>52</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>106</v>
@@ -11990,12 +11993,12 @@
         <v>10</v>
       </c>
       <c r="G476" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>107</v>
@@ -12004,7 +12007,7 @@
         <v>52</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>108</v>
@@ -12013,12 +12016,12 @@
         <v>10</v>
       </c>
       <c r="G477" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>109</v>
@@ -12027,7 +12030,7 @@
         <v>9</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E478" s="2" t="s">
         <v>110</v>
@@ -12036,12 +12039,12 @@
         <v>10</v>
       </c>
       <c r="G478" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>111</v>
@@ -12050,7 +12053,7 @@
         <v>9</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>112</v>
@@ -12059,12 +12062,12 @@
         <v>10</v>
       </c>
       <c r="G479" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>113</v>
@@ -12073,7 +12076,7 @@
         <v>9</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>114</v>
@@ -12082,12 +12085,12 @@
         <v>10</v>
       </c>
       <c r="G480" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>115</v>
@@ -12096,7 +12099,7 @@
         <v>9</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>116</v>
@@ -12105,12 +12108,12 @@
         <v>10</v>
       </c>
       <c r="G481" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>117</v>
@@ -12119,7 +12122,7 @@
         <v>9</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>118</v>
@@ -12128,12 +12131,12 @@
         <v>10</v>
       </c>
       <c r="G482" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>119</v>
@@ -12142,7 +12145,7 @@
         <v>52</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>120</v>
@@ -12151,12 +12154,12 @@
         <v>10</v>
       </c>
       <c r="G483" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>121</v>
@@ -12165,7 +12168,7 @@
         <v>52</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E484" s="2" t="s">
         <v>122</v>
@@ -12174,12 +12177,12 @@
         <v>10</v>
       </c>
       <c r="G484" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>123</v>
@@ -12188,7 +12191,7 @@
         <v>9</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>124</v>
@@ -12197,12 +12200,12 @@
         <v>10</v>
       </c>
       <c r="G485" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>125</v>
@@ -12211,7 +12214,7 @@
         <v>9</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>126</v>
@@ -12220,12 +12223,12 @@
         <v>10</v>
       </c>
       <c r="G486" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>127</v>
@@ -12234,7 +12237,7 @@
         <v>9</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E487" s="2" t="s">
         <v>128</v>
@@ -12243,12 +12246,12 @@
         <v>10</v>
       </c>
       <c r="G487" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>129</v>
@@ -12257,7 +12260,7 @@
         <v>9</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>130</v>
@@ -12266,12 +12269,12 @@
         <v>10</v>
       </c>
       <c r="G488" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>131</v>
@@ -12280,7 +12283,7 @@
         <v>9</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>132</v>
@@ -12289,12 +12292,12 @@
         <v>10</v>
       </c>
       <c r="G489" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>133</v>
@@ -12303,7 +12306,7 @@
         <v>9</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>134</v>
@@ -12312,12 +12315,12 @@
         <v>10</v>
       </c>
       <c r="G490" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>135</v>
@@ -12326,7 +12329,7 @@
         <v>9</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>136</v>
@@ -12335,12 +12338,12 @@
         <v>10</v>
       </c>
       <c r="G491" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>137</v>
@@ -12349,7 +12352,7 @@
         <v>9</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>138</v>
@@ -12358,12 +12361,12 @@
         <v>10</v>
       </c>
       <c r="G492" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>139</v>
@@ -12372,7 +12375,7 @@
         <v>9</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>140</v>
@@ -12381,12 +12384,12 @@
         <v>10</v>
       </c>
       <c r="G493" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>141</v>
@@ -12395,7 +12398,7 @@
         <v>52</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>142</v>
@@ -12404,12 +12407,12 @@
         <v>10</v>
       </c>
       <c r="G494" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>143</v>
@@ -12418,7 +12421,7 @@
         <v>52</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>144</v>
@@ -12427,21 +12430,21 @@
         <v>10</v>
       </c>
       <c r="G495" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>146</v>
@@ -12450,12 +12453,12 @@
         <v>10</v>
       </c>
       <c r="G496" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>213</v>
@@ -12464,7 +12467,7 @@
         <v>52</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>215</v>
@@ -12473,12 +12476,12 @@
         <v>10</v>
       </c>
       <c r="G497" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>217</v>
@@ -12487,7 +12490,7 @@
         <v>52</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>218</v>
@@ -12496,12 +12499,12 @@
         <v>10</v>
       </c>
       <c r="G498" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>219</v>
@@ -12510,7 +12513,7 @@
         <v>52</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>220</v>
@@ -12519,12 +12522,12 @@
         <v>10</v>
       </c>
       <c r="G499" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>221</v>
@@ -12533,7 +12536,7 @@
         <v>52</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>222</v>
@@ -12542,12 +12545,12 @@
         <v>10</v>
       </c>
       <c r="G500" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>223</v>
@@ -12556,7 +12559,7 @@
         <v>52</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E501" s="2" t="s">
         <v>224</v>
@@ -12565,12 +12568,12 @@
         <v>10</v>
       </c>
       <c r="G501" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>225</v>
@@ -12579,7 +12582,7 @@
         <v>52</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E502" s="2" t="s">
         <v>226</v>
@@ -12588,12 +12591,12 @@
         <v>10</v>
       </c>
       <c r="G502" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>227</v>
@@ -12602,7 +12605,7 @@
         <v>52</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>228</v>
@@ -12611,15 +12614,15 @@
         <v>10</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>52</v>
@@ -12628,7 +12631,7 @@
         <v>75</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F504" s="2" t="s">
         <v>10</v>
@@ -12639,10 +12642,10 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>52</v>
@@ -12651,7 +12654,7 @@
         <v>75</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F505" s="2" t="s">
         <v>10</v>
@@ -12662,10 +12665,10 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>52</v>
@@ -12674,7 +12677,7 @@
         <v>75</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F506" s="2" t="s">
         <v>10</v>
@@ -12685,10 +12688,10 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>52</v>
@@ -12697,7 +12700,7 @@
         <v>75</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F507" s="2" t="s">
         <v>10</v>
@@ -12708,10 +12711,10 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>52</v>
@@ -12720,7 +12723,7 @@
         <v>75</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F508" s="2" t="s">
         <v>10</v>
@@ -12731,10 +12734,10 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>52</v>
@@ -12743,7 +12746,7 @@
         <v>75</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F509" s="2" t="s">
         <v>10</v>
@@ -12754,10 +12757,10 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>52</v>
@@ -12766,7 +12769,7 @@
         <v>75</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F510" s="2" t="s">
         <v>10</v>
@@ -12777,10 +12780,10 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>52</v>
@@ -12789,7 +12792,7 @@
         <v>247</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F511" s="2" t="s">
         <v>10</v>
@@ -12800,10 +12803,10 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>52</v>
@@ -12812,7 +12815,7 @@
         <v>247</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F512" s="2" t="s">
         <v>10</v>
@@ -12823,10 +12826,10 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>9</v>
@@ -12835,10 +12838,10 @@
         <v>75</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F513" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G513" s="2" t="s">
         <v>55</v>
@@ -12846,10 +12849,10 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>9</v>
@@ -12858,7 +12861,7 @@
         <v>75</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F514" s="2" t="s">
         <v>10</v>
@@ -12869,19 +12872,19 @@
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F515" s="2" t="s">
         <v>10</v>
@@ -12892,19 +12895,19 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F516" s="2" t="s">
         <v>10</v>
@@ -12915,19 +12918,19 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F517" s="2" t="s">
         <v>10</v>
@@ -12938,19 +12941,19 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F518" s="2" t="s">
         <v>10</v>
